--- a/public/slip_template.xlsx
+++ b/public/slip_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\badbo\Downloads\logisys-step38-slip\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\badbo\Documents\logisys\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{791B4DAF-7299-49FF-A03A-CE2AAF4F577E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7248C6-8EB2-4C6C-AB5A-45E818FACD2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="2250" windowWidth="20865" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="765" yWindow="720" windowWidth="28035" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId1"/>
@@ -94,7 +94,7 @@
     <numFmt numFmtId="177" formatCode="0&quot;月&quot;"/>
     <numFmt numFmtId="178" formatCode="m/d"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,12 +181,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
       <b/>
       <sz val="36"/>
       <name val="游ゴシック"/>
@@ -619,7 +613,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -753,15 +747,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -771,7 +756,10 @@
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -781,17 +769,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1119,54 +1110,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
       <c r="D1"/>
       <c r="E1"/>
       <c r="F1"/>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
       <c r="L1"/>
-      <c r="M1" s="55">
+      <c r="M1" s="54">
         <v>36526</v>
       </c>
-      <c r="N1" s="53"/>
+      <c r="N1" s="51"/>
       <c r="O1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="56">
+      <c r="P1" s="55">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="48">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="45">
         <v>2000</v>
       </c>
-      <c r="D2" s="49">
+      <c r="D2" s="46">
         <v>1</v>
       </c>
-      <c r="E2" s="50">
+      <c r="E2" s="47">
         <v>1</v>
       </c>
       <c r="F2" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="P2" s="57"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="P2" s="56"/>
     </row>
     <row r="3" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="40"/>
@@ -1279,7 +1270,7 @@
     </row>
     <row r="6" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14"/>
-      <c r="B6" s="45"/>
+      <c r="B6" s="57"/>
       <c r="C6" s="20"/>
       <c r="D6" s="18"/>
       <c r="E6" s="28"/>
@@ -1297,7 +1288,7 @@
     </row>
     <row r="7" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="15"/>
-      <c r="B7" s="46"/>
+      <c r="B7" s="58"/>
       <c r="C7" s="21"/>
       <c r="D7" s="19"/>
       <c r="E7" s="32"/>
@@ -1315,7 +1306,7 @@
     </row>
     <row r="8" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="13"/>
-      <c r="B8" s="47"/>
+      <c r="B8" s="44"/>
       <c r="C8" s="22"/>
       <c r="D8" s="17"/>
       <c r="E8" s="25"/>
@@ -1333,7 +1324,7 @@
     </row>
     <row r="9" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14"/>
-      <c r="B9" s="45"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="20"/>
       <c r="D9" s="18"/>
       <c r="E9" s="28"/>
@@ -1351,7 +1342,7 @@
     </row>
     <row r="10" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="15"/>
-      <c r="B10" s="46"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="21"/>
       <c r="D10" s="19"/>
       <c r="E10" s="32"/>
@@ -1369,7 +1360,7 @@
     </row>
     <row r="11" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="13"/>
-      <c r="B11" s="47"/>
+      <c r="B11" s="44"/>
       <c r="C11" s="22"/>
       <c r="D11" s="17"/>
       <c r="E11" s="25"/>
@@ -1387,7 +1378,7 @@
     </row>
     <row r="12" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14"/>
-      <c r="B12" s="45"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="20"/>
       <c r="D12" s="18"/>
       <c r="E12" s="28"/>
@@ -1405,7 +1396,7 @@
     </row>
     <row r="13" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="15"/>
-      <c r="B13" s="46"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="21"/>
       <c r="D13" s="19"/>
       <c r="E13" s="32"/>
@@ -1423,7 +1414,7 @@
     </row>
     <row r="14" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="13"/>
-      <c r="B14" s="47"/>
+      <c r="B14" s="44"/>
       <c r="C14" s="22"/>
       <c r="D14" s="17"/>
       <c r="E14" s="25"/>
@@ -1441,7 +1432,7 @@
     </row>
     <row r="15" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14"/>
-      <c r="B15" s="45"/>
+      <c r="B15" s="57"/>
       <c r="C15" s="20"/>
       <c r="D15" s="18"/>
       <c r="E15" s="28"/>
@@ -1459,7 +1450,7 @@
     </row>
     <row r="16" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="15"/>
-      <c r="B16" s="46"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="21"/>
       <c r="D16" s="19"/>
       <c r="E16" s="32"/>
@@ -1477,7 +1468,7 @@
     </row>
     <row r="17" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="13"/>
-      <c r="B17" s="47"/>
+      <c r="B17" s="44"/>
       <c r="C17" s="22"/>
       <c r="D17" s="17"/>
       <c r="E17" s="25"/>
@@ -1495,7 +1486,7 @@
     </row>
     <row r="18" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14"/>
-      <c r="B18" s="45"/>
+      <c r="B18" s="57"/>
       <c r="C18" s="20"/>
       <c r="D18" s="18"/>
       <c r="E18" s="28"/>
@@ -1513,7 +1504,7 @@
     </row>
     <row r="19" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="15"/>
-      <c r="B19" s="46"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="21"/>
       <c r="D19" s="19"/>
       <c r="E19" s="32"/>
@@ -1531,7 +1522,7 @@
     </row>
     <row r="20" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="13"/>
-      <c r="B20" s="47"/>
+      <c r="B20" s="44"/>
       <c r="C20" s="22"/>
       <c r="D20" s="17"/>
       <c r="E20" s="25"/>
@@ -1549,7 +1540,7 @@
     </row>
     <row r="21" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14"/>
-      <c r="B21" s="45"/>
+      <c r="B21" s="57"/>
       <c r="C21" s="20"/>
       <c r="D21" s="18"/>
       <c r="E21" s="28"/>
@@ -1567,7 +1558,7 @@
     </row>
     <row r="22" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="15"/>
-      <c r="B22" s="46"/>
+      <c r="B22" s="58"/>
       <c r="C22" s="21"/>
       <c r="D22" s="19"/>
       <c r="E22" s="32"/>
@@ -1585,7 +1576,7 @@
     </row>
     <row r="23" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="13"/>
-      <c r="B23" s="47"/>
+      <c r="B23" s="44"/>
       <c r="C23" s="22"/>
       <c r="D23" s="17"/>
       <c r="E23" s="25"/>
@@ -1603,7 +1594,7 @@
     </row>
     <row r="24" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14"/>
-      <c r="B24" s="45"/>
+      <c r="B24" s="57"/>
       <c r="C24" s="20"/>
       <c r="D24" s="18"/>
       <c r="E24" s="28"/>
@@ -1621,7 +1612,7 @@
     </row>
     <row r="25" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="15"/>
-      <c r="B25" s="46"/>
+      <c r="B25" s="58"/>
       <c r="C25" s="21"/>
       <c r="D25" s="19"/>
       <c r="E25" s="32"/>
@@ -1639,7 +1630,7 @@
     </row>
     <row r="26" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="13"/>
-      <c r="B26" s="47"/>
+      <c r="B26" s="44"/>
       <c r="C26" s="22"/>
       <c r="D26" s="17"/>
       <c r="E26" s="25"/>
@@ -1657,7 +1648,7 @@
     </row>
     <row r="27" spans="1:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="14"/>
-      <c r="B27" s="45"/>
+      <c r="B27" s="57"/>
       <c r="C27" s="20"/>
       <c r="D27" s="18"/>
       <c r="E27" s="28"/>
@@ -1675,7 +1666,7 @@
     </row>
     <row r="28" spans="1:16" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A28" s="15"/>
-      <c r="B28" s="46"/>
+      <c r="B28" s="58"/>
       <c r="C28" s="21"/>
       <c r="D28" s="19"/>
       <c r="E28" s="32"/>
